--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Downtown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Downtown_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +454,14 @@
           <t>Cream Cheese</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>62.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>124.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E2" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Joe Tea - Ginseng Green</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.95</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Joe Tea - Half &amp; Half</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21.95</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Joe Tea - Peach</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>43.90</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E5" t="n">
+        <v>43.9</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Oat Milk</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>16.09</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>128.72</t>
-        </is>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="E6" t="n">
+        <v>128.72</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Poland Spring - Sport Top</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11.09</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Simply - Orange</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>44.33</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>44.33</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="E8" t="n">
+        <v>44.33</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Tuna - Ahi (Sesame Seared)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>174.60</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>174.60</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>174.6</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Yogurt - Plain (BIB)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>37.80</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>37.80</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>37.8</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Almond Milk</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>35.74</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>71.48</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="E11" t="n">
+        <v>71.48</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,56 @@
           <t>Spindrift - Lemon</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>24.83</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>24.83</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="E12" t="n">
+        <v>24.83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TN454</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TN362</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Pineapple</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13.38</v>
       </c>
     </row>
   </sheetData>
